--- a/astro-site/public/dl/catering-checklist-templates/01-catering-prep-production-checklist.xlsx
+++ b/astro-site/public/dl/catering-checklist-templates/01-catering-prep-production-checklist.xlsx
@@ -694,7 +694,7 @@
     <row r="10">
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>▸ Green cells are editable: assigned to, due by, notes.</t>
+          <t>▸ Green cells are editable: assigned to, time, notes.</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>Do the pre-cooking: confit, braises, sous-vide</t>
+          <t>Do the pre-cooking: confit, braises, sous-vide. Cool anything made ahead in shallow pans, an ice bath or the blast chiller: 135 °F to 70 °F within 2 h, then to 41 °F within 4 h more (FDA Food Code 3-501.14), and log it</t>
         </is>
       </c>
       <c r="C32" s="14" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>Pre-plate cold starters and canapes</t>
+          <t>Pre-plate cold appetizers and canapés</t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr">
@@ -1999,7 +1999,7 @@
   </mergeCells>
   <conditionalFormatting sqref="A6:G51">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>$E6="✓"</formula>
+      <formula>AND($E6="✓",$B6&lt;&gt;"Task")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">

--- a/astro-site/public/dl/catering-checklist-templates/01-catering-prep-production-checklist.xlsx
+++ b/astro-site/public/dl/catering-checklist-templates/01-catering-prep-production-checklist.xlsx
@@ -727,9 +727,9 @@
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>▸ Fish served raw or undercooked (ceviche, tartare, marinated, cold-smoked) needs parasite destruction first: frozen at −4 °F or below for 7 days, or at −31 °F or below until solid plus 15 h (FDA Food Code 3-402.11). Ask the supplier for the freezing record, keep it 90 days and note the lot.</t>
+      <c r="B16" s="25" t="inlineStr">
+        <is>
+          <t>▸ Fish served raw or undercooked (ceviche, tartare, marinated, cold-smoked) needs parasite destruction first: frozen and stored at −4 °F or below for 7 days; or frozen at −31 °F or below until solid and stored at −31 °F or below for 15 h; or frozen at −31 °F or below until solid and stored at −4 °F or below for 24 h (FDA Food Code 3-402.11). Ask the supplier for the freezing record, keep it 90 days (FDA Food Code 3-402.12) and note the lot.</t>
         </is>
       </c>
     </row>
@@ -1376,7 +1376,7 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>Fish served raw or undercooked (ceviche, tartare, marinated, cold-smoked) — parasite destruction: get the supplier's freezing record (−4 °F or below for 7 days, or −31 °F or below until solid + 15 h; FDA Food Code 3-402.11) or freeze it yourself, keep the record 90 days and note the lot</t>
+          <t>Fish served raw or undercooked (ceviche, tartare, marinated, cold-smoked) — parasite destruction: get the supplier's freezing record (−4 °F or below for 7 days; or −31 °F or below until solid, then 15 h at −31 °F or below or 24 h at −4 °F or below; FDA Food Code 3-402.11) or freeze it yourself, keep the record 90 days (FDA Food Code 3-402.12) and note the lot</t>
         </is>
       </c>
       <c r="C34" s="14" t="inlineStr">
